--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,11 +440,10 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -645,6 +644,9 @@
     <t>Permet de définir le niveau d'effort (au repos, à l'effort, après l'effort) lors de la mesure de la fréquence respiratoire</t>
   </si>
   <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
     <t>Observation.extension:supportingInfo</t>
   </si>
   <si>
@@ -675,7 +677,7 @@
   </si>
   <si>
     <t>Motif de la mesure
-Texte libre (ex. infection, insolation, vaccination…)</t>
+Texte libre (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -4661,7 +4663,7 @@
         <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4747,13 +4749,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>113</v>
@@ -4775,13 +4777,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>117</v>
@@ -4869,13 +4871,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>80</v>
@@ -4897,13 +4899,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4989,10 +4991,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5018,16 +5020,16 @@
         <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -5076,7 +5078,7 @@
         <v>120</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5111,10 +5113,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5137,17 +5139,17 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5196,7 +5198,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5211,19 +5213,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5231,14 +5233,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5257,19 +5259,19 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5318,7 +5320,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5330,19 +5332,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5353,14 +5355,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5379,16 +5381,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5438,7 +5440,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5450,19 +5452,19 @@
         <v>103</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5473,10 +5475,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5502,16 +5504,16 @@
         <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5536,13 +5538,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5560,7 +5562,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5575,19 +5577,19 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5595,10 +5597,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5621,19 +5623,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5661,16 +5663,16 @@
         <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5680,7 +5682,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5701,13 +5703,13 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5715,13 +5717,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>80</v>
@@ -5743,19 +5745,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5783,10 +5785,10 @@
         <v>175</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5804,7 +5806,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5825,13 +5827,13 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5839,10 +5841,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5957,10 +5959,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6077,10 +6079,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6106,16 +6108,16 @@
         <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -6164,7 +6166,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -6185,10 +6187,10 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -6199,10 +6201,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6317,10 +6319,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6437,10 +6439,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6466,23 +6468,23 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>80</v>
@@ -6524,7 +6526,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6545,10 +6547,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6559,10 +6561,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6588,13 +6590,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6644,7 +6646,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6665,10 +6667,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6679,10 +6681,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6708,23 +6710,23 @@
         <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>80</v>
@@ -6766,7 +6768,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6787,10 +6789,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6801,10 +6803,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6830,16 +6832,16 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6888,7 +6890,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6909,10 +6911,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6923,10 +6925,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6949,19 +6951,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -7010,7 +7012,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -7031,10 +7033,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -7045,10 +7047,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7074,16 +7076,16 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -7132,7 +7134,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7153,10 +7155,10 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -7167,14 +7169,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7193,19 +7195,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -7233,10 +7235,10 @@
         <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -7254,7 +7256,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -7269,30 +7271,30 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7407,10 +7409,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7527,10 +7529,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7556,16 +7558,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7602,7 +7604,7 @@
         <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7612,7 +7614,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7633,10 +7635,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7647,13 +7649,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>80</v>
@@ -7678,16 +7680,16 @@
         <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7736,7 +7738,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7757,10 +7759,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7771,10 +7773,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7889,10 +7891,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8009,10 +8011,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8038,23 +8040,23 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>80</v>
@@ -8096,7 +8098,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -8117,10 +8119,10 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8133,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8160,13 +8162,13 @@
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8216,7 +8218,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8237,10 +8239,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -8251,10 +8253,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8280,23 +8282,23 @@
         <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>80</v>
@@ -8338,7 +8340,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8359,10 +8361,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -8373,10 +8375,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8402,16 +8404,16 @@
         <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8460,7 +8462,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8481,10 +8483,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8495,10 +8497,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8521,19 +8523,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8582,7 +8584,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8603,10 +8605,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8617,10 +8619,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8646,16 +8648,16 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8704,7 +8706,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8725,10 +8727,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8739,10 +8741,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8765,19 +8767,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8826,7 +8828,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8838,22 +8840,22 @@
         <v>103</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8861,10 +8863,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8887,16 +8889,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8946,7 +8948,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8958,7 +8960,7 @@
         <v>103</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -8967,13 +8969,13 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8981,14 +8983,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9007,19 +9009,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -9068,7 +9070,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -9080,22 +9082,22 @@
         <v>103</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -9103,14 +9105,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9129,19 +9131,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9190,7 +9192,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9199,25 +9201,25 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9225,10 +9227,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9254,13 +9256,13 @@
         <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9310,7 +9312,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9331,13 +9333,13 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9345,10 +9347,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9371,19 +9373,19 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9432,7 +9434,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9444,22 +9446,22 @@
         <v>103</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9467,10 +9469,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9493,19 +9495,19 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9542,17 +9544,17 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9561,7 +9563,7 @@
         <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -9570,30 +9572,30 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>80</v>
@@ -9615,19 +9617,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9637,7 +9639,7 @@
         <v>80</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>80</v>
@@ -9676,7 +9678,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9685,7 +9687,7 @@
         <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9694,27 +9696,27 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9829,10 +9831,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9949,10 +9951,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9975,19 +9977,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -10036,7 +10038,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -10057,10 +10059,10 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -10071,10 +10073,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10100,22 +10102,22 @@
         <v>171</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>80</v>
@@ -10136,13 +10138,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -10160,7 +10162,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10181,10 +10183,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10195,10 +10197,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10224,16 +10226,16 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10282,7 +10284,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10303,10 +10305,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10317,10 +10319,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10346,23 +10348,23 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>80</v>
@@ -10404,7 +10406,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10413,7 +10415,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>104</v>
@@ -10425,10 +10427,10 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10439,10 +10441,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10468,16 +10470,16 @@
         <v>171</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10502,13 +10504,13 @@
         <v>80</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>80</v>
@@ -10526,7 +10528,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10547,10 +10549,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10561,10 +10563,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10587,19 +10589,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10627,10 +10629,10 @@
         <v>151</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10648,7 +10650,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10657,7 +10659,7 @@
         <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10672,7 +10674,7 @@
         <v>105</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10683,10 +10685,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10801,10 +10803,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10921,10 +10923,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10950,16 +10952,16 @@
         <v>147</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -11008,7 +11010,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -11029,10 +11031,10 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -11043,10 +11045,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11161,10 +11163,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11281,10 +11283,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11310,16 +11312,16 @@
         <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11368,7 +11370,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11389,10 +11391,10 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -11403,10 +11405,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11432,13 +11434,13 @@
         <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11488,7 +11490,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11509,10 +11511,10 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -11523,10 +11525,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11552,16 +11554,16 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11610,7 +11612,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11631,10 +11633,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11645,10 +11647,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11674,16 +11676,16 @@
         <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11732,7 +11734,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11753,10 +11755,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11767,10 +11769,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11793,19 +11795,19 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11854,7 +11856,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11875,10 +11877,10 @@
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11889,10 +11891,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11918,16 +11920,16 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11976,7 +11978,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11997,10 +11999,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -12011,14 +12013,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12037,19 +12039,19 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -12078,7 +12080,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -12096,7 +12098,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -12114,27 +12116,27 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12157,19 +12159,19 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12218,7 +12220,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12239,10 +12241,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12253,10 +12255,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12279,16 +12281,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12314,11 +12316,11 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12336,7 +12338,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12354,27 +12356,27 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12489,10 +12491,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12609,10 +12611,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12638,16 +12640,16 @@
         <v>147</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12696,7 +12698,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12717,10 +12719,10 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12731,10 +12733,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12849,10 +12851,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12969,10 +12971,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12998,16 +13000,16 @@
         <v>135</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13056,7 +13058,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13077,10 +13079,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13091,10 +13093,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13120,13 +13122,13 @@
         <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13176,7 +13178,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13197,10 +13199,10 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13211,10 +13213,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13240,16 +13242,16 @@
         <v>171</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13298,7 +13300,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13319,10 +13321,10 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13333,10 +13335,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13362,16 +13364,16 @@
         <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13420,7 +13422,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13441,10 +13443,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13455,10 +13457,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13481,19 +13483,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13542,7 +13544,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13563,10 +13565,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13577,10 +13579,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13606,16 +13608,16 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13664,7 +13666,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13685,10 +13687,10 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13699,10 +13701,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13725,19 +13727,19 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13762,13 +13764,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13786,7 +13788,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13807,10 +13809,10 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13821,10 +13823,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13939,10 +13941,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14059,10 +14061,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14088,16 +14090,16 @@
         <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14146,7 +14148,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14167,10 +14169,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14181,10 +14183,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14299,10 +14301,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14419,10 +14421,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14448,16 +14450,16 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14506,7 +14508,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14527,10 +14529,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14541,10 +14543,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14570,13 +14572,13 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14626,7 +14628,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14647,10 +14649,10 @@
         <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14661,10 +14663,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14690,16 +14692,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14748,7 +14750,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14769,10 +14771,10 @@
         <v>80</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14783,10 +14785,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14812,16 +14814,16 @@
         <v>107</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14870,7 +14872,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14891,10 +14893,10 @@
         <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14905,10 +14907,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14931,19 +14933,19 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14992,7 +14994,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -15013,10 +15015,10 @@
         <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -15027,10 +15029,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15056,16 +15058,16 @@
         <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15114,7 +15116,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15135,10 +15137,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15149,10 +15151,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15175,16 +15177,16 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15234,7 +15236,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15246,33 +15248,33 @@
         <v>103</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15295,16 +15297,16 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15354,7 +15356,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15366,33 +15368,33 @@
         <v>103</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15415,19 +15417,19 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -15476,7 +15478,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15488,7 +15490,7 @@
         <v>103</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
@@ -15497,10 +15499,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15511,10 +15513,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15629,10 +15631,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15749,14 +15751,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15778,16 +15780,16 @@
         <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
@@ -15836,7 +15838,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15871,10 +15873,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15897,16 +15899,16 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15956,7 +15958,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15965,10 +15967,10 @@
         <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>80</v>
@@ -15977,10 +15979,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15991,10 +15993,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16017,16 +16019,16 @@
         <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16076,7 +16078,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -16085,10 +16087,10 @@
         <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>80</v>
@@ -16097,10 +16099,10 @@
         <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -16111,10 +16113,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16137,19 +16139,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16177,10 +16179,10 @@
         <v>175</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -16198,7 +16200,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16216,13 +16218,13 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16233,10 +16235,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16259,19 +16261,19 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -16299,10 +16301,10 @@
         <v>161</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16320,7 +16322,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16338,13 +16340,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16355,10 +16357,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16381,19 +16383,19 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16442,7 +16444,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16454,7 +16456,7 @@
         <v>103</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
@@ -16463,10 +16465,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16477,10 +16479,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16506,13 +16508,13 @@
         <v>107</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16562,7 +16564,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16583,10 +16585,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16597,10 +16599,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16623,16 +16625,16 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16682,7 +16684,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16694,7 +16696,7 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -16703,10 +16705,10 @@
         <v>80</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16717,10 +16719,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16743,16 +16745,16 @@
         <v>92</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16802,7 +16804,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16814,7 +16816,7 @@
         <v>103</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>80</v>
@@ -16823,10 +16825,10 @@
         <v>80</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>80</v>
@@ -16837,10 +16839,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16863,19 +16865,19 @@
         <v>92</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>80</v>
@@ -16924,7 +16926,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16936,7 +16938,7 @@
         <v>103</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>80</v>
@@ -16945,10 +16947,10 @@
         <v>80</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>80</v>
@@ -16959,10 +16961,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17077,10 +17079,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17197,14 +17199,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -17226,16 +17228,16 @@
         <v>114</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17284,7 +17286,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17319,10 +17321,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17345,19 +17347,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17385,10 +17387,10 @@
         <v>151</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>80</v>
@@ -17406,7 +17408,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>91</v>
@@ -17424,16 +17426,16 @@
         <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17441,10 +17443,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17467,19 +17469,19 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17504,13 +17506,13 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>80</v>
@@ -17528,7 +17530,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17537,7 +17539,7 @@
         <v>91</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>104</v>
@@ -17546,27 +17548,27 @@
         <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17589,19 +17591,19 @@
         <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17629,10 +17631,10 @@
         <v>151</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>80</v>
@@ -17650,7 +17652,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17659,7 +17661,7 @@
         <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>104</v>
@@ -17674,7 +17676,7 @@
         <v>105</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
@@ -17685,14 +17687,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17711,19 +17713,19 @@
         <v>80</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
@@ -17751,28 +17753,28 @@
         <v>151</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17790,27 +17792,27 @@
         <v>80</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17836,16 +17838,16 @@
         <v>81</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17894,7 +17896,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17915,10 +17917,10 @@
         <v>80</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>

--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
